--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23619.75</v>
+        <v>23498.39</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31453.63</v>
+        <v>31124.24</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3814.19</v>
+        <v>3774.25</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1408.77</v>
+        <v>1418.53</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2352.08</v>
+        <v>2368.68</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5790.92</v>
+        <v>5716.07</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>32124.28</v>
+        <v>32054.76</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7916.59</v>
+        <v>7883.4</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5869.45</v>
+        <v>5891.98</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7056.01</v>
+        <v>7074.72</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1669.89</v>
+        <v>1674.32</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21670.59</v>
+        <v>21640.19</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>899.77</v>
+        <v>900.92</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6915.36</v>
+        <v>6753.59</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2752.72</v>
+        <v>2717.78</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4836.24</v>
+        <v>4842.95</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2824.04</v>
+        <v>2822.11</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3824.63</v>
+        <v>3882.85</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10812.39</v>
+        <v>11075.32</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3807.55</v>
+        <v>3920.72</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12035</v>
+        <v>11992.15</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4897.65</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21734.66</v>
+        <v>21797.62</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6918.33</v>
+        <v>6938.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4881.37</v>
+        <v>4860.79</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4468.73</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19509.34</v>
+        <v>19683.1</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4345.62</v>
+        <v>4384.32</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1308.69</v>
+        <v>1320.35</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9318.139999999999</v>
+        <v>9308.530000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1159.38</v>
+        <v>1158.18</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>918.02</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>43905.97</v>
+        <v>43639.18</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>821.85</v>
+        <v>818.6799999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2127.64</v>
+        <v>2129.69</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1646.22</v>
+        <v>1673.36</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2542.52</v>
+        <v>2584.42</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>839.03</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32540.74</v>
+        <v>33050.47</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2153.96</v>
+        <v>2144.33</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1078.04</v>
+        <v>1073.22</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>40755.22</v>
+        <v>40923.57</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1686.86</v>
+        <v>1682.21</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4275.18</v>
+        <v>4225.83</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4812.69</v>
+        <v>4781.86</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>776.96</v>
+        <v>760.24</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1636.65</v>
+        <v>1598.56</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3794.8</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1672.42</v>
+        <v>1628.38</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>838.27</v>
+        <v>816.2</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2124.63</v>
+        <v>2130.82</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2725.29</v>
+        <v>2736.62</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1369.75</v>
+        <v>1385.33</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>794.24</v>
+        <v>799.3200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>15159.74</v>
+        <v>15256.7</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6135.29</v>
+        <v>6174.53</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2319.61</v>
+        <v>2324.41</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1062.51</v>
+        <v>1064.72</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4301.03</v>
+        <v>4275.26</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4738.06</v>
+        <v>4697.65</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>28402.02</v>
+        <v>28554.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>982.53</v>
+        <v>993.52</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1324.4</v>
+        <v>1339.21</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1960.5</v>
+        <v>1975.35</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1364.9</v>
+        <v>1370.07</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25236.92</v>
+        <v>24985.24</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1104.47</v>
+        <v>1093.45</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2356.62</v>
+        <v>2330.98</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>788.75</v>
+        <v>780.17</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1189.34</v>
+        <v>1195.18</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>968.86</v>
+        <v>972.08</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2467.08</v>
+        <v>2474.93</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10753.63</v>
+        <v>10854.49</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5498.32</v>
+        <v>5549.89</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1116.8</v>
+        <v>1108.33</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5223.02</v>
+        <v>5183.4</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1659.37</v>
+        <v>1635.82</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4939.76</v>
+        <v>4909.13</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>800.9299999999999</v>
+        <v>816.16</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1015.16</v>
+        <v>1034.46</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2917.25</v>
+        <v>2983.04</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1246.98</v>
+        <v>1275.1</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>895.08</v>
+        <v>883.16</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1828.93</v>
+        <v>1801.83</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7234.47</v>
+        <v>7127.28</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4966.3</v>
+        <v>4892.72</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1151.95</v>
+        <v>1156.45</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>779.21</v>
+        <v>783.1799999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2175.56</v>
+        <v>2170.83</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>56021.89</v>
+        <v>55697.63</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3792.28</v>
+        <v>3731.09</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>10136</v>
+        <v>9972.42</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>868.66</v>
+        <v>858.5599999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6018.19</v>
+        <v>5948.17</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1218.59</v>
+        <v>1211.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707412-111-CM25</t>
+          <t>1407-15112-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>23498.39</v>
+        <v>2759.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2404-1477-CM25</t>
+          <t>838102-38-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31124.24</v>
+        <v>2368.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2404-1478-CM25</t>
+          <t>1350296-776-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3774.25</v>
+        <v>6758.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2404-1557-CM25</t>
+          <t>1350296-1538-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1418.53</v>
+        <v>3505.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>707412-131-CM25</t>
+          <t>1350296-1829-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2368.68</v>
+        <v>7641.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1346281-201-CM25</t>
+          <t>707412-111-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5716.07</v>
+        <v>23498.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2404-1642-CM25</t>
+          <t>2404-1477-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>32054.76</v>
+        <v>31124.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1350296-2521-CM25</t>
+          <t>2404-1478-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>winkler limitada</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7883.4</v>
+        <v>3774.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>628-494-CM25</t>
+          <t>2404-1557-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5891.98</v>
+        <v>1418.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3145-688-CM25</t>
+          <t>707412-131-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7074.72</v>
+        <v>2368.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>548847-87-CM25</t>
+          <t>1346281-201-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1674.32</v>
+        <v>5716.07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2404-1757-CM25</t>
+          <t>2404-1642-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21640.19</v>
+        <v>32054.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>948-353-CM25</t>
+          <t>1350296-2521-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DISMER, INTEGRAL SERVICES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.003.691-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>900.92</v>
+        <v>7883.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3352-1-CM26</t>
+          <t>628-494-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6753.59</v>
+        <v>5891.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1350296-18-CM26</t>
+          <t>548847-87-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2717.78</v>
+        <v>1674.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>838102-7-CM26</t>
+          <t>3145-688-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Iª Brigada Aérea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4842.95</v>
+        <v>7074.72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1091793-8-CM26</t>
+          <t>2404-1757-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2822.11</v>
+        <v>21640.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1350296-2-CM26</t>
+          <t>948-353-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISMER, INTEGRAL SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.003.691-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3882.85</v>
+        <v>900.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1350296-67-CM26</t>
+          <t>3352-1-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>11075.32</v>
+        <v>6753.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1346281-26-CM26</t>
+          <t>1350296-18-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>winkler limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3920.72</v>
+        <v>2717.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057448-18-CM26</t>
+          <t>838102-7-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11992.15</v>
+        <v>4842.95</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1346281-28-CM26</t>
+          <t>1091793-8-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.710-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4861</v>
+        <v>2822.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3170-10-CM26</t>
+          <t>1350296-2-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>21797.62</v>
+        <v>3882.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2013-103-CM26</t>
+          <t>1350296-67-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6938.37</v>
+        <v>11075.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1350296-228-CM26</t>
+          <t>1346281-26-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4860.79</v>
+        <v>3920.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1171177-7-CM26</t>
+          <t>1057448-18-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4481</v>
+        <v>11992.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2013-150-CM26</t>
+          <t>1346281-28-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19683.1</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3170-22-CM26</t>
+          <t>2013-103-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4384.32</v>
+        <v>6938.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3170-23-CM26</t>
+          <t>3170-10-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1320.35</v>
+        <v>21797.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>907562-7-CM26</t>
+          <t>1350296-228-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>9308.530000000001</v>
+        <v>4860.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1407-59-CM26</t>
+          <t>1171177-7-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,22 +2359,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Centro de Educación y Trabajo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1158.18</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1070620-1945-CM26</t>
+          <t>2013-150-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>913.02</v>
+        <v>19683.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>707412-16-CM26</t>
+          <t>3170-22-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.057.703-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>43639.18</v>
+        <v>4384.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1227-50-CM26</t>
+          <t>3170-23-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>818.6799999999999</v>
+        <v>1320.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>618472-3-CM26</t>
+          <t>907562-7-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2129.69</v>
+        <v>9308.530000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1350296-360-CM26</t>
+          <t>1407-59-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1673.36</v>
+        <v>1158.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1350296-361-CM26</t>
+          <t>1070620-1945-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2584.42</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5690-21-CM26</t>
+          <t>707412-16-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>852.86</v>
+        <v>43639.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1426404-6-CM26</t>
+          <t>1227-50-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>33050.47</v>
+        <v>818.6799999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>614-8-CM26</t>
+          <t>618472-3-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2144.33</v>
+        <v>2129.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1407-116-CM26</t>
+          <t>1350296-360-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1073.22</v>
+        <v>1673.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1426397-83-CM26</t>
+          <t>1350296-361-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>40923.57</v>
+        <v>2584.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3159-31-CM26</t>
+          <t>5690-21-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1682.21</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3352-38-CM26</t>
+          <t>1426404-6-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4225.83</v>
+        <v>33050.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3349-63-CM26</t>
+          <t>614-8-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4781.86</v>
+        <v>2144.33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>935934-62-CM26</t>
+          <t>1407-116-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>760.24</v>
+        <v>1073.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>935934-63-CM26</t>
+          <t>1426397-83-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1598.56</v>
+        <v>40923.57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1346281-51-CM26</t>
+          <t>3159-31-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3673.8</v>
+        <v>1682.21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>548847-9-CM26</t>
+          <t>3352-38-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1628.38</v>
+        <v>4225.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>696217-28-CM26</t>
+          <t>3349-63-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>816.2</v>
+        <v>4781.86</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3159-50-CM26</t>
+          <t>935934-62-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,27 +3574,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2130.82</v>
+        <v>760.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3352-54-CM26</t>
+          <t>935934-63-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2736.62</v>
+        <v>1598.56</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3352-55-CM26</t>
+          <t>1346281-51-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1385.33</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>838102-52-CM26</t>
+          <t>548847-9-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>799.3200000000001</v>
+        <v>1628.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2404-470-CM26</t>
+          <t>696217-28-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>15256.7</v>
+        <v>816.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2404-471-CM26</t>
+          <t>3159-50-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6174.53</v>
+        <v>2130.82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5690-51-CM26</t>
+          <t>3352-54-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2324.41</v>
+        <v>2736.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>935934-94-CM26</t>
+          <t>3352-55-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1064.72</v>
+        <v>1385.33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5126-39-CM26</t>
+          <t>838102-52-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>Zona Bienestar "Iquique" Bienestar Social</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4275.26</v>
+        <v>799.3200000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>628-29-CM26</t>
+          <t>2404-470-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,27 +4123,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4697.65</v>
+        <v>15256.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>707412-38-CM26</t>
+          <t>2404-471-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>28554.96</v>
+        <v>6174.53</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1350296-871-CM26</t>
+          <t>935934-94-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>Zona de Bienestar Iquique</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>993.52</v>
+        <v>1064.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1350296-872-CM26</t>
+          <t>5690-51-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1339.21</v>
+        <v>2324.41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3159-64-CM26</t>
+          <t>5126-39-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1975.35</v>
+        <v>4275.26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1350296-897-CM26</t>
+          <t>628-29-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.906.980-8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1370.07</v>
+        <v>4697.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2404-600-CM26</t>
+          <t>707412-38-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>24985.24</v>
+        <v>28554.96</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3352-87-CM26</t>
+          <t>1350296-871-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1093.45</v>
+        <v>993.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3352-82-CM26</t>
+          <t>1350296-872-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2330.98</v>
+        <v>1339.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5690-56-CM26</t>
+          <t>3159-64-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>780.17</v>
+        <v>1975.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1091793-115-CM26</t>
+          <t>1350296-897-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1195.18</v>
+        <v>1370.07</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3170-86-CM26</t>
+          <t>2404-600-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>972.08</v>
+        <v>24985.24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057448-191-CM26</t>
+          <t>3352-87-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2474.93</v>
+        <v>1093.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3447-1597-CM26</t>
+          <t>3352-82-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10854.49</v>
+        <v>2330.98</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1346281-87-CM26</t>
+          <t>5690-56-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5549.89</v>
+        <v>780.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3349-191-CM26</t>
+          <t>1091793-115-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>62.000.710-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1108.33</v>
+        <v>1195.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1350296-1029-CM26</t>
+          <t>3170-86-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CENTRO DE ABASTECIMIENTO (I)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5183.4</v>
+        <v>972.08</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1407-330-CM26</t>
+          <t>1057448-191-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1635.82</v>
+        <v>2474.93</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2013-966-CM26</t>
+          <t>3447-1597-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4909.13</v>
+        <v>10854.49</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>696217-54-CM26</t>
+          <t>1346281-87-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>816.16</v>
+        <v>5549.89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5651-62-CM26</t>
+          <t>3349-191-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1034.46</v>
+        <v>1108.33</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>548847-30-CM26</t>
+          <t>1350296-1029-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2983.04</v>
+        <v>5183.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3352-110-CM26</t>
+          <t>1407-330-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,22 +5470,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1275.1</v>
+        <v>1635.82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1350296-1116-CM26</t>
+          <t>2013-966-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>883.16</v>
+        <v>4909.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1346281-97-CM26</t>
+          <t>696217-54-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,22 +5592,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1801.83</v>
+        <v>816.16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1350296-1122-CM26</t>
+          <t>5651-62-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>7127.28</v>
+        <v>1034.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1057448-246-CM26</t>
+          <t>548847-30-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4892.72</v>
+        <v>2983.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1057448-230-CM26</t>
+          <t>3352-110-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1156.45</v>
+        <v>1275.1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1346281-106-CM26</t>
+          <t>1350296-1116-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>783.1799999999999</v>
+        <v>883.16</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5690-94-CM26</t>
+          <t>1350296-1122-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2170.83</v>
+        <v>7127.28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>707412-54-CM26</t>
+          <t>1057448-246-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>55697.63</v>
+        <v>4892.72</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1407-432-CM26</t>
+          <t>1346281-97-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,27 +6014,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3731.09</v>
+        <v>1801.83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3447-2075-CM26</t>
+          <t>1057448-230-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>9972.42</v>
+        <v>1156.45</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1091793-149-CM26</t>
+          <t>1346281-106-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>858.5599999999999</v>
+        <v>783.1799999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1350296-1344-CM26</t>
+          <t>5690-94-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5948.17</v>
+        <v>2170.83</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3159-115-CM26</t>
+          <t>707412-54-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,6 +6303,311 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
+        <v>55697.63</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1407-432-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Iquique</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Comercial Agustin Limitada</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>3731.09</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3447-2075-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.265.100-6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>LOGISTRA SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>78.209.481-5</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>9972.42</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1350296-1344-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>FLEXING CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.592.530-4</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>5948.17</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1091793-149-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>62.000.710-2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>858.5599999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3159-115-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>61.102.038-4</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LOGISTRA SPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.209.481-5</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
         <v>1211.83</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M191"/>
+  <dimension ref="A1:M202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3170-21-CM25</t>
+          <t>3170-20-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>13006.01</v>
+        <v>25763.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3170-20-CM25</t>
+          <t>3170-21-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25763.2</v>
+        <v>13006.01</v>
       </c>
     </row>
     <row r="14">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1213005-42-CM25</t>
+          <t>1213005-40-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5735.57</v>
+        <v>10614.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1213005-41-CM25</t>
+          <t>1213005-42-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2538.76</v>
+        <v>5735.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1213005-40-CM25</t>
+          <t>1213005-41-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10614.93</v>
+        <v>2538.76</v>
       </c>
     </row>
     <row r="19">
@@ -1856,7 +1856,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>707412-12-CM25</t>
+          <t>5651-19-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3034.86</v>
+        <v>2339.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5651-19-CM25</t>
+          <t>707412-12-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2339.92</v>
+        <v>3034.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1171177-21-CM25</t>
+          <t>1260687-82-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>50.937.880-0</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6938.24</v>
+        <v>7103.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1260687-82-CM25</t>
+          <t>1171177-21-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>50.937.880-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7103.51</v>
+        <v>6938.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3159-39-CM25</t>
+          <t>2013-256-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8061.76</v>
+        <v>7241.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2013-256-CM25</t>
+          <t>3159-39-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7241.8</v>
+        <v>8061.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1419450-16-CM25</t>
+          <t>908366-14-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.938.800-2</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>61533.63</v>
+        <v>2503.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>908366-14-CM25</t>
+          <t>1419450-16-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2503.87</v>
+        <v>61533.63</v>
       </c>
     </row>
     <row r="32">
@@ -2893,7 +2893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>575924-44-CM25</t>
+          <t>575924-46-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3559.33</v>
+        <v>7849.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>575924-46-CM25</t>
+          <t>575924-44-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7849.46</v>
+        <v>3559.33</v>
       </c>
     </row>
     <row r="43">
@@ -3625,7 +3625,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3352-166-CM25</t>
+          <t>1346281-92-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3299.27</v>
+        <v>4947.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1346281-92-CM25</t>
+          <t>3352-166-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4947.78</v>
+        <v>3299.27</v>
       </c>
     </row>
     <row r="55">
@@ -3869,7 +3869,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1350296-1268-CM25</t>
+          <t>1260687-225-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>71.497.400-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4175.63</v>
+        <v>8176.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1260687-225-CM25</t>
+          <t>1350296-1268-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>71.497.400-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE POZO ALMONTE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8176.8</v>
+        <v>4175.63</v>
       </c>
     </row>
     <row r="59">
@@ -4235,7 +4235,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>707412-60-CM25</t>
+          <t>1350296-1538-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14185.46</v>
+        <v>3505.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1350296-1538-CM25</t>
+          <t>707412-60-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3505.64</v>
+        <v>14185.46</v>
       </c>
     </row>
     <row r="65">
@@ -5699,7 +5699,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2404-1477-CM25</t>
+          <t>2404-1478-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>31124.24</v>
+        <v>3774.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2404-1478-CM25</t>
+          <t>2404-1477-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3774.25</v>
+        <v>31124.24</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2404-1557-CM25</t>
+          <t>1417913-601-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL ARIA LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.076.237-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1418.53</v>
+        <v>11510.56</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>707412-131-CM25</t>
+          <t>2404-1557-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2368.68</v>
+        <v>1418.53</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1346281-201-CM25</t>
+          <t>707412-131-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5716.07</v>
+        <v>2368.68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2404-1642-CM25</t>
+          <t>1417913-632-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>32054.76</v>
+        <v>63535.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1350296-2521-CM25</t>
+          <t>1346281-201-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7883.4</v>
+        <v>5716.07</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>628-494-CM25</t>
+          <t>2404-1642-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,22 +6141,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5891.98</v>
+        <v>32054.76</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>548847-87-CM25</t>
+          <t>1350296-2521-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1674.32</v>
+        <v>7883.4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3145-688-CM25</t>
+          <t>548847-87-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6268,17 +6268,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.103.023-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7074.72</v>
+        <v>1674.32</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2404-1757-CM25</t>
+          <t>3145-688-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.103.023-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>21640.19</v>
+        <v>7074.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>948-353-CM25</t>
+          <t>2404-1757-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,22 +6385,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.901.003-7</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Secretaría Regional Ministerial de Educación de la Primera Región</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DISMER, INTEGRAL SERVICES LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.003.691-9</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>900.92</v>
+        <v>21640.19</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3352-1-CM26</t>
+          <t>948-353-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>60.901.003-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISMER, INTEGRAL SERVICES LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.003.691-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6753.59</v>
+        <v>900.92</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1350296-18-CM26</t>
+          <t>3352-1-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>winkler limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2717.78</v>
+        <v>6753.59</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>838102-7-CM26</t>
+          <t>1350296-18-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4842.95</v>
+        <v>2717.78</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1091793-8-CM26</t>
+          <t>838102-7-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2822.11</v>
+        <v>4842.95</v>
       </c>
     </row>
     <row r="103">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2013-150-CM26</t>
+          <t>1417913-124-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>19683.1</v>
+        <v>9364.940000000001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3170-22-CM26</t>
+          <t>3170-23-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4384.32</v>
+        <v>1320.35</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3170-23-CM26</t>
+          <t>3170-22-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>78.057.703-7</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1320.35</v>
+        <v>4384.32</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1407-59-CM26</t>
+          <t>2013-150-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1158.18</v>
+        <v>19683.1</v>
       </c>
     </row>
     <row r="116">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7529,7 +7529,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1070620-1945-CM26</t>
+          <t>1407-59-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +7544,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.000.530-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>913.02</v>
+        <v>1158.18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>707412-16-CM26</t>
+          <t>1070620-1945-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +7605,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.530-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL DOCTOR ERNESTO TORRES GALDAMES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>43639.18</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1227-50-CM26</t>
+          <t>707412-16-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.804.002-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE IQUIQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>818.6799999999999</v>
+        <v>43639.18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>618472-3-CM26</t>
+          <t>1227-50-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.979.990-9</t>
+          <t>60.804.002-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2129.69</v>
+        <v>818.6799999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1350296-360-CM26</t>
+          <t>618472-3-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.990-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1673.36</v>
+        <v>2129.69</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1350296-361-CM26</t>
+          <t>1350296-360-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2584.42</v>
+        <v>1673.36</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5690-21-CM26</t>
+          <t>1350296-361-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>852.86</v>
+        <v>2584.42</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1426404-6-CM26</t>
+          <t>5690-21-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>33050.47</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1407-116-CM26</t>
+          <t>1426404-6-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1073.22</v>
+        <v>33050.47</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>614-8-CM26</t>
+          <t>1407-116-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2144.33</v>
+        <v>1073.22</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1426397-83-CM26</t>
+          <t>614-8-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.980.910-6</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Iquique</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>40923.57</v>
+        <v>2144.33</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3159-31-CM26</t>
+          <t>1426397-83-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.980.910-6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>Servicio Local de Educación Pública Iquique</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1682.21</v>
+        <v>40923.57</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3352-38-CM26</t>
+          <t>3159-31-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4225.83</v>
+        <v>1682.21</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3349-63-CM26</t>
+          <t>3352-38-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>4781.86</v>
+        <v>4225.83</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>935934-62-CM26</t>
+          <t>3349-63-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>760.24</v>
+        <v>4781.86</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>935934-63-CM26</t>
+          <t>935934-62-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1598.56</v>
+        <v>760.24</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1346281-51-CM26</t>
+          <t>935934-63-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3673.8</v>
+        <v>1598.56</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>696217-28-CM26</t>
+          <t>1346281-51-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>816.2</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="135">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8688,7 +8688,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3159-50-CM26</t>
+          <t>696217-28-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2130.82</v>
+        <v>816.2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3352-54-CM26</t>
+          <t>3159-50-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8764,22 +8764,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2736.62</v>
+        <v>2130.82</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3352-55-CM26</t>
+          <t>3352-54-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1385.33</v>
+        <v>2736.62</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>838102-52-CM26</t>
+          <t>3352-55-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Iquique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>799.3200000000001</v>
+        <v>1385.33</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2404-470-CM26</t>
+          <t>838102-52-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8952,17 +8952,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>15256.7</v>
+        <v>799.3200000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2404-471-CM26</t>
+          <t>2404-470-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6174.53</v>
+        <v>15256.7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5690-51-CM26</t>
+          <t>2404-471-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2324.41</v>
+        <v>6174.53</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>935934-94-CM26</t>
+          <t>5690-51-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Iquique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1064.72</v>
+        <v>2324.41</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5126-39-CM26</t>
+          <t>935934-94-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.979.650-0</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4275.26</v>
+        <v>1064.72</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>628-29-CM26</t>
+          <t>5126-39-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.979.650-0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.906.980-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4697.65</v>
+        <v>4275.26</v>
       </c>
     </row>
     <row r="146">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9603,7 +9603,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2404-600-CM26</t>
+          <t>3352-87-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9623,17 +9623,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>24985.24</v>
+        <v>1093.45</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3352-87-CM26</t>
+          <t>2404-600-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9684,17 +9684,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1093.45</v>
+        <v>24985.24</v>
       </c>
     </row>
     <row r="153">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9847,7 +9847,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1091793-115-CM26</t>
+          <t>1305552-63-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1195.18</v>
+        <v>8079.88</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3170-86-CM26</t>
+          <t>1305552-68-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>61.981.030-9</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (I)</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA TAMARUGAL</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>972.08</v>
+        <v>3092.81</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1057448-191-CM26</t>
+          <t>3170-86-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2474.93</v>
+        <v>972.08</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3447-1597-CM26</t>
+          <t>1057448-191-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10040,12 +10040,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>10854.49</v>
+        <v>2474.93</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1346281-87-CM26</t>
+          <t>1417913-341-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10101,27 +10101,27 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5549.89</v>
+        <v>4138.99</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3349-191-CM26</t>
+          <t>3447-1597-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1108.33</v>
+        <v>10854.49</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1350296-1029-CM26</t>
+          <t>1346281-87-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5183.4</v>
+        <v>5549.89</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1407-330-CM26</t>
+          <t>3349-191-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,22 +10289,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1635.82</v>
+        <v>1108.33</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2013-966-CM26</t>
+          <t>1350296-1029-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4909.13</v>
+        <v>5183.4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>696217-54-CM26</t>
+          <t>1407-330-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,22 +10411,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>816.16</v>
+        <v>1635.82</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5651-62-CM26</t>
+          <t>2013-966-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,22 +10472,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1034.46</v>
+        <v>4909.13</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>548847-30-CM26</t>
+          <t>5358-157-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,22 +10533,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2983.04</v>
+        <v>2272.7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3352-110-CM26</t>
+          <t>696217-54-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1275.1</v>
+        <v>816.16</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1350296-1116-CM26</t>
+          <t>5651-62-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>883.16</v>
+        <v>1034.46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1350296-1122-CM26</t>
+          <t>548847-30-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7127.28</v>
+        <v>2983.04</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1057448-246-CM26</t>
+          <t>3352-110-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>4892.72</v>
+        <v>1275.1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1346281-97-CM26</t>
+          <t>1350296-1116-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1801.83</v>
+        <v>883.16</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1057448-230-CM26</t>
+          <t>1350296-1122-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1156.45</v>
+        <v>7127.28</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1346281-106-CM26</t>
+          <t>1057448-246-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>783.1799999999999</v>
+        <v>4892.72</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5690-94-CM26</t>
+          <t>1346281-97-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2170.83</v>
+        <v>1801.83</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>707412-54-CM26</t>
+          <t>1057448-230-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>55697.63</v>
+        <v>1156.45</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1407-432-CM26</t>
+          <t>1346281-106-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,22 +11143,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3731.09</v>
+        <v>783.1799999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3447-2075-CM26</t>
+          <t>1417913-534-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>70.938.800-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9972.42</v>
+        <v>13472.35</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1350296-1344-CM26</t>
+          <t>5690-94-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,22 +11265,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5948.17</v>
+        <v>2170.83</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1091793-149-CM26</t>
+          <t>707412-54-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>62.000.710-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DESARROLLO SUSTENTABLE DE LA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>858.5599999999999</v>
+        <v>55697.63</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3159-115-CM26</t>
+          <t>1407-432-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.102.038-4</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1211.83</v>
+        <v>3731.09</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3352-141-CM26</t>
+          <t>3447-2075-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>972.5599999999999</v>
+        <v>9972.42</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>696217-95-CM26</t>
+          <t>1350296-1344-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11504,12 +11504,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>784.08</v>
+        <v>5948.17</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2013-1277-CM26</t>
+          <t>3159-115-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.102.038-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>9949.719999999999</v>
+        <v>1211.83</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5651-78-CM26</t>
+          <t>3352-141-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1010.6</v>
+        <v>972.5599999999999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>614-27-CM26</t>
+          <t>696217-95-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,22 +11692,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1491.02</v>
+        <v>784.08</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2013-1318-CM26</t>
+          <t>2013-1277-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4631.36</v>
+        <v>9949.719999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1350296-1505-CM26</t>
+          <t>5651-78-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3896.27</v>
+        <v>1010.6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1350296-1506-CM26</t>
+          <t>614-27-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6418.15</v>
+        <v>1491.02</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3349-290-CM26</t>
+          <t>2013-1318-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1624.48</v>
+        <v>4631.36</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3352-164-CM26</t>
+          <t>1350296-1505-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1440.37</v>
+        <v>3896.27</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3352-166-CM26</t>
+          <t>1350296-1506-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,22 +12058,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,7 +12098,678 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
+        <v>6418.15</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>3349-290-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>65.283.230-K</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>1624.48</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>3352-164-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>1440.37</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>3352-166-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
         <v>1012.66</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1417913-631-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>18124.24</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1407-540-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>828.85</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>548847-56-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1549.34</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>699-27-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>2269.55</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>3352-176-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.101.024-9</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>2462.4</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1417913-771-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>70.938.800-2</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>11374.38</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>5690-135-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>2916.24</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>696217-149-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>831.6799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2143,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2208,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2273,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2338,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2907,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3354,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3484,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3549,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3870,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4122,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4187,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4630,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4756,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4821,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5134,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5447,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5764,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5829,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5894,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5959,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6085,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6211,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6341,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6532,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6780,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6845,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6910,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6975,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7101,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7227,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7292,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7357,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7422,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7552,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7678,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7743,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7869,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7995,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8552,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8617,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8682,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8808,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8873,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8938,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9125,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9190,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9572,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9637,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9702,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9828,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9893,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9958,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10023,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10088,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10153,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10283,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10348,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10413,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10478,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10604,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10734,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10982,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11230,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11356,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11421,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11551,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11616,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11681,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11746,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11811,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11937,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12063,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12372,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12498,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12563,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12689,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12815,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13067,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13193,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -757,7 +757,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1074,7 +1078,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1265,7 +1273,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1391,7 +1403,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1635,7 +1651,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2017,7 +2037,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2533,7 +2557,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2716,7 +2744,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3163,7 +3195,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3744,7 +3780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3935,7 +3975,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4695,7 +4739,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5264,7 +5312,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5703,7 +5755,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8121,7 +8177,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8182,7 +8242,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8430,7 +8494,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10860,7 +10928,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11876,7 +11948,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12628,7 +12704,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M202"/>
+  <dimension ref="A1:M215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7300,7 +7300,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2013-103-CM26</t>
+          <t>3170-10-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7320,17 +7320,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7359,13 +7359,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>6938.37</v>
+        <v>21797.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3170-10-CM26</t>
+          <t>2013-103-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7385,17 +7385,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>21797.62</v>
+        <v>6938.37</v>
       </c>
     </row>
     <row r="110">
@@ -7625,7 +7625,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3170-23-CM26</t>
+          <t>3170-22-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7665,28 +7665,32 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+          <t>78.057.703-7</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1320.35</v>
+        <v>4384.32</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3170-22-CM26</t>
+          <t>2013-150-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7706,17 +7710,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.941.300-8</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7726,17 +7730,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7745,13 +7749,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4384.32</v>
+        <v>19683.1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2013-150-CM26</t>
+          <t>3170-23-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7771,17 +7775,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.941.300-8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7791,32 +7795,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>19683.1</v>
+        <v>1320.35</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>907562-7-CM26</t>
+          <t>1407-59-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.010.400-8</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7856,28 +7856,32 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>9308.530000000001</v>
+        <v>1158.18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1407-59-CM26</t>
+          <t>907562-7-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7897,17 +7901,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>69.010.400-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PICA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7917,26 +7921,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1158.18</v>
+        <v>9308.530000000001</v>
       </c>
     </row>
     <row r="118">
@@ -8194,7 +8194,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1350296-360-CM26</t>
+          <t>1350296-361-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8234,17 +8234,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8253,13 +8253,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1673.36</v>
+        <v>2584.42</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1350296-361-CM26</t>
+          <t>5690-21-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8299,32 +8299,28 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2584.42</v>
+        <v>852.86</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5690-21-CM26</t>
+          <t>1350296-360-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8349,12 +8345,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8364,22 +8360,26 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>852.86</v>
+        <v>1673.36</v>
       </c>
     </row>
     <row r="125">
@@ -8446,7 +8446,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1407-116-CM26</t>
+          <t>614-8-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.004.002-0</t>
+          <t>61.802.001-0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8486,32 +8486,28 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1073.22</v>
+        <v>2144.33</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>614-8-CM26</t>
+          <t>1407-116-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8536,12 +8532,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.802.001-0</t>
+          <t>61.004.002-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8551,22 +8547,26 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2144.33</v>
+        <v>1073.22</v>
       </c>
     </row>
     <row r="128">
@@ -9336,7 +9336,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>838102-52-CM26</t>
+          <t>2404-471-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>799.3200000000001</v>
+        <v>6174.53</v>
       </c>
     </row>
     <row r="141">
@@ -9462,7 +9462,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2404-471-CM26</t>
+          <t>838102-52-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9482,17 +9482,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9521,13 +9521,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6174.53</v>
+        <v>799.3200000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5690-51-CM26</t>
+          <t>935934-94-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.770-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9586,13 +9586,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2324.41</v>
+        <v>1064.72</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>935934-94-CM26</t>
+          <t>5690-51-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.980.770-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1064.72</v>
+        <v>2324.41</v>
       </c>
     </row>
     <row r="145">
@@ -9787,7 +9787,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1350296-871-CM26</t>
+          <t>1350296-872-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9827,28 +9827,32 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>78.203.286-0</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>993.52</v>
+        <v>1339.21</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1350296-872-CM26</t>
+          <t>1350296-871-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9888,26 +9892,22 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1339.21</v>
+        <v>993.52</v>
       </c>
     </row>
     <row r="149">
@@ -10043,7 +10043,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3352-87-CM26</t>
+          <t>2404-600-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10063,17 +10063,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>69.010.300-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -10102,13 +10102,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1093.45</v>
+        <v>24985.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2404-600-CM26</t>
+          <t>3352-87-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10128,17 +10128,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.010.300-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>24985.24</v>
+        <v>1093.45</v>
       </c>
     </row>
     <row r="153">
@@ -10624,7 +10624,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3447-1597-CM26</t>
+          <t>1346281-87-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10664,17 +10664,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10683,13 +10683,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>10854.49</v>
+        <v>5549.89</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1346281-87-CM26</t>
+          <t>3447-1597-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.481-5</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10748,13 +10748,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5549.89</v>
+        <v>10854.49</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3349-191-CM26</t>
+          <t>1350296-1029-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>65.283.230-K</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10794,32 +10794,28 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.592.530-4</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1108.33</v>
+        <v>5183.4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1350296-1029-CM26</t>
+          <t>3349-191-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10844,12 +10840,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>65.283.230-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10859,22 +10855,26 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5183.4</v>
+        <v>1108.33</v>
       </c>
     </row>
     <row r="164">
@@ -11071,7 +11071,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>696217-54-CM26</t>
+          <t>5651-62-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>816.16</v>
+        <v>1034.46</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5651-62-CM26</t>
+          <t>696217-54-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11152,17 +11152,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -11187,13 +11187,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1034.46</v>
+        <v>816.16</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>548847-30-CM26</t>
+          <t>3352-110-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11233,28 +11233,32 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>78.212.867-1</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2983.04</v>
+        <v>1275.1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3352-110-CM26</t>
+          <t>548847-30-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11279,12 +11283,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11294,26 +11298,22 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1275.1</v>
+        <v>2983.04</v>
       </c>
     </row>
     <row r="171">
@@ -11380,7 +11380,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1350296-1122-CM26</t>
+          <t>1346281-97-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7127.28</v>
+        <v>1801.83</v>
       </c>
     </row>
     <row r="173">
@@ -11510,7 +11510,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1346281-97-CM26</t>
+          <t>1350296-1122-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11535,12 +11535,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1801.83</v>
+        <v>7127.28</v>
       </c>
     </row>
     <row r="175">
@@ -12156,7 +12156,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3352-141-CM26</t>
+          <t>696217-95-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12176,17 +12176,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>972.5599999999999</v>
+        <v>784.08</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>696217-95-CM26</t>
+          <t>3352-141-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12237,17 +12237,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>784.08</v>
+        <v>972.5599999999999</v>
       </c>
     </row>
     <row r="186">
@@ -12721,7 +12721,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3352-164-CM26</t>
+          <t>3352-166-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12761,32 +12761,28 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1440.37</v>
+        <v>1012.66</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3352-166-CM26</t>
+          <t>3352-164-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12826,22 +12822,26 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1012.66</v>
+        <v>1440.37</v>
       </c>
     </row>
     <row r="195">
@@ -12977,7 +12977,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>548847-56-CM26</t>
+          <t>3352-176-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13002,12 +13002,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.101.024-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13017,22 +13017,26 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1549.34</v>
+        <v>2462.4</v>
       </c>
     </row>
     <row r="198">
@@ -13099,7 +13103,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3352-176-CM26</t>
+          <t>548847-56-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13119,17 +13123,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.101.024-9</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13139,26 +13143,22 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2462.4</v>
+        <v>1549.34</v>
       </c>
     </row>
     <row r="200">
@@ -13346,6 +13346,831 @@
       </c>
       <c r="M202" s="2" t="n">
         <v>831.6799999999999</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1346281-150-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>9321.540000000001</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>935934-236-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.980.770-7</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1350296-1875-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>4246.75</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1350296-1876-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>WINKLER LIMITADA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>79.722.860-5</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>7863.94</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2013-1619-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>9.454.737-7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>15198.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2404-1296-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>9.454.737-7</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>16519.07</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2404-1295-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>69.010.300-1</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>18031.87</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>792895-22-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>61.980.220-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA NENE SPA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>76.067.436-2</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>1138.14</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1350296-1926-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>65.228.694-1</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>FLEXING CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>76.592.530-4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>3443.91</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>838102-111-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>1646.26</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>838102-105-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>73.923.800-5</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>1526.76</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1407-651-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.004.002-0</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>MAKRON CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>78.209.499-8</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>1220.59</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1057448-511-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>61.606.100-3</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>3279.96</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/tarapaca.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
